--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
@@ -36,169 +36,169 @@
     <t xml:space="preserve">Metropolitana</t>
   </si>
   <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lampa</t>
   </si>
   <si>
-    <t xml:space="preserve">Ñuñoa</t>
+    <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
     <t xml:space="preserve">Buin</t>
   </si>
   <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Hurtado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alhué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Monte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
-    <t xml:space="preserve">Padre Hurtado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curacaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Monte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alhué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiltil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñaflor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Joaquín</t>
   </si>
   <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Macul</t>
   </si>
   <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
   </si>
   <si>
     <t xml:space="preserve">La Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">Lo Espejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Prado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
-    <t xml:space="preserve">Calera de Tango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
   </si>
   <si>
     <t xml:space="preserve">San Bernardo</t>
   </si>
   <si>
-    <t xml:space="preserve">La Pintana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Bosque</t>
-  </si>
-  <si>
     <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recoleta</t>
-  </si>
-  <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
     <t xml:space="preserve">Puente Alto</t>
   </si>
   <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:47</t>
+    <t xml:space="preserve">2026-09-24 00:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -625,13 +625,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>13302</v>
+        <v>13123</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13488</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="3">
@@ -642,13 +642,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>13120</v>
+        <v>13114</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11779</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="4">
@@ -659,13 +659,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13402</v>
+        <v>13115</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9794</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="5">
@@ -676,13 +676,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>13130</v>
+        <v>13120</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7525</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="6">
@@ -693,13 +693,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>13604</v>
+        <v>13302</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6698</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="7">
@@ -710,13 +710,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>13123</v>
+        <v>13603</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5279</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="8">
@@ -727,13 +727,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>13301</v>
+        <v>13402</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5108</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="9">
@@ -744,13 +744,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>13404</v>
+        <v>13132</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4239</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="10">
@@ -761,13 +761,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>13114</v>
+        <v>13604</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3678</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="11">
@@ -778,13 +778,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>13603</v>
+        <v>13301</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2922</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -795,13 +795,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>13503</v>
+        <v>13601</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2069</v>
+        <v>995</v>
       </c>
     </row>
     <row r="13">
@@ -812,13 +812,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>13115</v>
+        <v>13404</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1726</v>
+        <v>975</v>
       </c>
     </row>
     <row r="14">
@@ -829,13 +829,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>13109</v>
+        <v>13202</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1448</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15">
@@ -846,13 +846,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>13505</v>
+        <v>13107</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1410</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16">
@@ -863,13 +863,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>13501</v>
+        <v>13505</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1232</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17">
@@ -880,13 +880,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13601</v>
+        <v>13203</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>902</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18">
@@ -897,13 +897,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13203</v>
+        <v>13504</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>734</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
@@ -914,13 +914,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>13504</v>
+        <v>13113</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>569</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -931,13 +931,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>13602</v>
+        <v>13303</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>355</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
@@ -948,13 +948,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>13202</v>
+        <v>13503</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>116</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -971,7 +971,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>79</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="23">
@@ -982,13 +982,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>13303</v>
+        <v>13602</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-689</v>
+        <v>-139</v>
       </c>
     </row>
     <row r="24">
@@ -999,13 +999,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13102</v>
+        <v>13501</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-1161</v>
+        <v>-142</v>
       </c>
     </row>
     <row r="25">
@@ -1016,13 +1016,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>13605</v>
+        <v>13109</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-2191</v>
+        <v>-170</v>
       </c>
     </row>
     <row r="26">
@@ -1033,13 +1033,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>13107</v>
+        <v>13102</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-2698</v>
+        <v>-427</v>
       </c>
     </row>
     <row r="27">
@@ -1050,13 +1050,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>13132</v>
+        <v>13605</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-2946</v>
+        <v>-764</v>
       </c>
     </row>
     <row r="28">
@@ -1067,13 +1067,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13129</v>
+        <v>13111</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-3127</v>
+        <v>-780</v>
       </c>
     </row>
     <row r="29">
@@ -1084,13 +1084,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>13118</v>
+        <v>13121</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-3606</v>
+        <v>-898</v>
       </c>
     </row>
     <row r="30">
@@ -1101,13 +1101,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>13113</v>
+        <v>13130</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-4038</v>
+        <v>-926</v>
       </c>
     </row>
     <row r="31">
@@ -1118,13 +1118,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>13131</v>
+        <v>13129</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-5548</v>
+        <v>-1108</v>
       </c>
     </row>
     <row r="32">
@@ -1135,13 +1135,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>13110</v>
+        <v>13131</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-6767</v>
+        <v>-1532</v>
       </c>
     </row>
     <row r="33">
@@ -1152,13 +1152,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>13116</v>
+        <v>13108</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-6951</v>
+        <v>-1639</v>
       </c>
     </row>
     <row r="34">
@@ -1169,13 +1169,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>13111</v>
+        <v>13118</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-7192</v>
+        <v>-1721</v>
       </c>
     </row>
     <row r="35">
@@ -1186,13 +1186,13 @@
         <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>13121</v>
+        <v>13116</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-7489</v>
+        <v>-1756</v>
       </c>
     </row>
     <row r="36">
@@ -1203,13 +1203,13 @@
         <v>40</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>13117</v>
+        <v>13403</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-7847</v>
+        <v>-1865</v>
       </c>
     </row>
     <row r="37">
@@ -1220,13 +1220,13 @@
         <v>41</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>13103</v>
+        <v>13117</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-8302</v>
+        <v>-1943</v>
       </c>
     </row>
     <row r="38">
@@ -1237,13 +1237,13 @@
         <v>42</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>13104</v>
+        <v>13122</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-8797</v>
+        <v>-2029</v>
       </c>
     </row>
     <row r="39">
@@ -1254,13 +1254,13 @@
         <v>43</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>13403</v>
+        <v>13103</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-9012</v>
+        <v>-2227</v>
       </c>
     </row>
     <row r="40">
@@ -1277,7 +1277,7 @@
         <v>2023</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-9043</v>
+        <v>-2349</v>
       </c>
     </row>
     <row r="41">
@@ -1288,13 +1288,13 @@
         <v>45</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13108</v>
+        <v>13127</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-9194</v>
+        <v>-2372</v>
       </c>
     </row>
     <row r="42">
@@ -1305,13 +1305,13 @@
         <v>46</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>13128</v>
+        <v>13112</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>-9203</v>
+        <v>-2599</v>
       </c>
     </row>
     <row r="43">
@@ -1322,13 +1322,13 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13401</v>
+        <v>13125</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>-10722</v>
+        <v>-2672</v>
       </c>
     </row>
     <row r="44">
@@ -1339,13 +1339,13 @@
         <v>48</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>13112</v>
+        <v>13128</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-10800</v>
+        <v>-2779</v>
       </c>
     </row>
     <row r="45">
@@ -1356,13 +1356,13 @@
         <v>49</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>13105</v>
+        <v>13110</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-11255</v>
+        <v>-2920</v>
       </c>
     </row>
     <row r="46">
@@ -1373,13 +1373,13 @@
         <v>50</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>13106</v>
+        <v>13104</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>-11333</v>
+        <v>-3169</v>
       </c>
     </row>
     <row r="47">
@@ -1390,13 +1390,13 @@
         <v>51</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>13125</v>
+        <v>13105</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>-11612</v>
+        <v>-3186</v>
       </c>
     </row>
     <row r="48">
@@ -1413,7 +1413,7 @@
         <v>2023</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>-12291</v>
+        <v>-4056</v>
       </c>
     </row>
     <row r="49">
@@ -1424,13 +1424,13 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13122</v>
+        <v>13401</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>-13850</v>
+        <v>-4150</v>
       </c>
     </row>
     <row r="50">
@@ -1441,13 +1441,13 @@
         <v>54</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>13127</v>
+        <v>13106</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>-14830</v>
+        <v>-5164</v>
       </c>
     </row>
     <row r="51">
@@ -1464,7 +1464,7 @@
         <v>2023</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>-30572</v>
+        <v>-7228</v>
       </c>
     </row>
     <row r="52">
@@ -1475,13 +1475,13 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13201</v>
+        <v>13119</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>-33762</v>
+        <v>-7986</v>
       </c>
     </row>
     <row r="53">
@@ -1492,13 +1492,13 @@
         <v>57</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>13119</v>
+        <v>13201</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>-34976</v>
+        <v>-8220</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:25</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:24</t>
+    <t xml:space="preserve">2026-10-05 08:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
